--- a/models/downapp.xlsx
+++ b/models/downapp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/dapi/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBC1CFA-E986-C94B-85A3-F85D9C3419A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8289FF8C-DC2A-6E44-B3CF-4F4589511359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
   <si>
     <t>name</t>
   </si>
@@ -292,6 +292,14 @@
   </si>
   <si>
     <t>加密密钥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orgid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属机构</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -861,9 +869,18 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="7"/>
+      <c r="A7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:8">

--- a/models/downapp.xlsx
+++ b/models/downapp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/dapi/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8289FF8C-DC2A-6E44-B3CF-4F4589511359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88896E5-65B5-E54F-8E29-9691FAD09DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G5" s="8"/>
     </row>
@@ -899,7 +899,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
